--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104707_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104707_W28.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7637</v>
+        <v>8.4382</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0603</v>
+        <v>7.4135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7034</v>
+        <v>1.0247</v>
       </c>
       <c r="G2" t="n">
-        <v>8.2895</v>
+        <v>8.273199999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2886</v>
+        <v>4.2799</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0009</v>
+        <v>3.9933</v>
       </c>
       <c r="J2" t="n">
-        <v>7.392</v>
+        <v>7.3406</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7479</v>
+        <v>4.7122</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6441</v>
+        <v>2.6285</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8975</v>
+        <v>0.9326</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4593</v>
+        <v>-0.4323</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3568</v>
+        <v>1.3648</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1913</v>
+        <v>-0.4888</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9557</v>
+        <v>-0.5323</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2356</v>
+        <v>0.0435</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0418</v>
+        <v>4.0675</v>
       </c>
       <c r="E3" t="n">
-        <v>2.987</v>
+        <v>3.2525</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0547</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4395</v>
+        <v>6.4331</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3317</v>
+        <v>3.3398</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1079</v>
+        <v>3.0933</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4625</v>
+        <v>5.4283</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0824</v>
+        <v>3.0682</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3802</v>
+        <v>2.3602</v>
       </c>
       <c r="M3" t="n">
-        <v>0.977</v>
+        <v>1.0048</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2493</v>
+        <v>0.2716</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0517</v>
+        <v>-0.0289</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9557</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.904</v>
+        <v>0.6218</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4864</v>
+        <v>3.4817</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8181</v>
+        <v>2.8054</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6683</v>
+        <v>0.6763</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7744</v>
+        <v>0.7779</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6998</v>
+        <v>0.7035</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6807</v>
+        <v>0.6778</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1391</v>
+        <v>0.1394</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3478</v>
+        <v>0.3485</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4724</v>
+        <v>-1.0324</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0578</v>
+        <v>0.8922</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5302</v>
+        <v>-1.9245</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1359</v>
+        <v>-0.1393</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8397</v>
+        <v>0.8441</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9756</v>
+        <v>-0.9835</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7042</v>
+        <v>1.6637</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2672</v>
+        <v>1.2476</v>
       </c>
       <c r="L5" t="n">
-        <v>0.437</v>
+        <v>0.4162</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8401</v>
+        <v>-1.8031</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4275</v>
+        <v>-0.4034</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2438</v>
+        <v>-0.8035</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6049</v>
+        <v>-0.7229</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3611</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3321</v>
+        <v>-1.1948</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.395</v>
+        <v>-0.3962</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9371</v>
+        <v>-0.7986</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7448</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3001</v>
+        <v>0.3042</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0449</v>
+        <v>-1.0426</v>
       </c>
       <c r="J6" t="n">
-        <v>0.092</v>
+        <v>0.0917</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8368</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5607</v>
+        <v>-0.4367</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4869</v>
+        <v>-0.4879</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7392</v>
+        <v>-1.555</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0803</v>
+        <v>0.3239</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6589</v>
+        <v>-1.8789</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4524</v>
+        <v>0.4609</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0885</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3732</v>
+        <v>0.3724</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5226</v>
+        <v>1.5064</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4431</v>
+        <v>0.4342</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0702</v>
+        <v>-1.0455</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0309</v>
+        <v>0.1418</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4688</v>
+        <v>-0.0444</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4379</v>
+        <v>0.1862</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.269</v>
+        <v>-2.7352</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1602</v>
+        <v>-1.8778</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1088</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3753</v>
+        <v>-2.3552</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3648</v>
+        <v>0.3811</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.7401</v>
+        <v>-2.7363</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9878</v>
+        <v>-0.9967</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3875</v>
+        <v>-1.3585</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0959</v>
+        <v>-0.5865</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5989</v>
+        <v>-0.1072</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6947</v>
+        <v>-0.4793</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5352</v>
+        <v>-2.9285</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.333</v>
+        <v>-2.1366</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2022</v>
+        <v>-0.7919</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9389</v>
+        <v>-1.93</v>
       </c>
       <c r="H9" t="n">
-        <v>1.401</v>
+        <v>1.4097</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.3399</v>
+        <v>-3.3397</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1363</v>
+        <v>0.1167</v>
       </c>
       <c r="K9" t="n">
-        <v>1.749</v>
+        <v>1.7409</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6127</v>
+        <v>-1.6242</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0752</v>
+        <v>-2.0467</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8062</v>
+        <v>-1.1986</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2521</v>
+        <v>-1.0178</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5541</v>
+        <v>-0.1808</v>
       </c>
       <c r="V9" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5077</v>
+        <v>-4.4424</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1969</v>
+        <v>-2.1621</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3108</v>
+        <v>-2.2803</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0294</v>
+        <v>-2.0357</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0187</v>
+        <v>-2.0191</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0107</v>
+        <v>-0.0166</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6386</v>
+        <v>-1.6624</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.372</v>
+        <v>-1.3864</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3908</v>
+        <v>-0.3733</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2268</v>
+        <v>-0.1579</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6775</v>
+        <v>-0.6088</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4506</v>
+        <v>0.4509</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0942</v>
+        <v>-5.4092</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2567</v>
+        <v>-2.5675</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8375</v>
+        <v>-2.8417</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4406</v>
+        <v>-0.4293</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0005</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0319</v>
+        <v>2.0202</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9524</v>
+        <v>0.948</v>
       </c>
       <c r="L11" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4725</v>
+        <v>-2.4496</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1364</v>
+        <v>-0.18</v>
       </c>
       <c r="T11" t="n">
-        <v>0.248</v>
+        <v>-0.0351</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1116</v>
+        <v>-0.1449</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.657899999999997</v>
+        <v>-3.310099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.501099999999999</v>
+        <v>5.547299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.1591</v>
+        <v>-8.8573</v>
       </c>
       <c r="G12" t="n">
-        <v>8.290900000000001</v>
+        <v>8.3172</v>
       </c>
       <c r="H12" t="n">
-        <v>9.2774</v>
+        <v>9.331200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9863999999999999</v>
+        <v>-1.014099999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>16.3958</v>
+        <v>16.1863</v>
       </c>
       <c r="K12" t="n">
-        <v>11.8917</v>
+        <v>11.7816</v>
       </c>
       <c r="L12" t="n">
-        <v>4.504099999999999</v>
+        <v>4.404999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.104900000000001</v>
+        <v>-7.8692</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.6143</v>
+        <v>-2.4503</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.4905</v>
+        <v>-5.4192</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.7443</v>
+        <v>-14.7962</v>
       </c>
       <c r="R12" t="n">
-        <v>9.0733</v>
+        <v>9.1053</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.9318</v>
+        <v>-3.5997</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.7634</v>
+        <v>-4.4162</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8315999999999998</v>
+        <v>0.8164</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3462</v>
+        <v>-2.3366</v>
       </c>
       <c r="W12" t="n">
-        <v>8.613099999999999</v>
+        <v>8.572800000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.9591</v>
+        <v>-10.9096</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4421</v>
+        <v>5.2623</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4198</v>
+        <v>5.133</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0223</v>
+        <v>0.1293</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9332</v>
+        <v>1.9185</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7998</v>
+        <v>1.7735</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1334</v>
+        <v>0.145</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9815</v>
+        <v>3.9376</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1232</v>
+        <v>3.0812</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0484</v>
+        <v>-2.0191</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R13" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S13" t="n">
-        <v>1.247</v>
+        <v>1.0788</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4779</v>
+        <v>0.2457</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7691</v>
+        <v>0.8331</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0064</v>
+        <v>-0.0113</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2968</v>
+        <v>3.2089</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5816</v>
+        <v>1.5701</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7152</v>
+        <v>1.6388</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1674</v>
+        <v>1.1675</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1414</v>
+        <v>-0.1435</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3088</v>
+        <v>1.311</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3482</v>
+        <v>1.3383</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1808</v>
+        <v>-0.1708</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6179</v>
+        <v>0.5261</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2994</v>
+        <v>0.3017</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3185</v>
+        <v>0.2243</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6041</v>
+        <v>0.6049</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4434</v>
+        <v>0.4471</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1449</v>
+        <v>1.0504</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4338</v>
+        <v>0.4223</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7111</v>
+        <v>0.628</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7608</v>
+        <v>-2.7765</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7821</v>
+        <v>-3.4031</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0213</v>
+        <v>0.6267</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8512</v>
+        <v>-0.6283</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8139</v>
+        <v>-2.1244</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>1.496</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-2.1481</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0318</v>
+        <v>-1.2788</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0586</v>
+        <v>-0.8694</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0646</v>
+        <v>0.5097</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7168</v>
+        <v>-0.465</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3478</v>
+        <v>0.9747</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.8814</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0656</v>
+        <v>0.9106</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8666</v>
+        <v>0.1923</v>
       </c>
       <c r="F16" t="n">
-        <v>0.199</v>
+        <v>0.7184</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9779</v>
+        <v>0.762</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7274</v>
+        <v>0.7813</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2505</v>
+        <v>-0.0193</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1105</v>
+        <v>0.8474</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2251</v>
+        <v>0.8101</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1147</v>
+        <v>0.0372</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0884</v>
+        <v>-0.0854</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9525</v>
+        <v>-0.0289</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1359</v>
+        <v>-0.0565</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9093</v>
+        <v>0.8316</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7561</v>
+        <v>0.483</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1532</v>
+        <v>0.3485</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6894</v>
+        <v>0.5329</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4784</v>
+        <v>1.7502</v>
       </c>
       <c r="F17" t="n">
-        <v>0.211</v>
+        <v>-1.2174</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7611</v>
+        <v>-4.4445</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.3981</v>
+        <v>-2.2026</v>
       </c>
       <c r="I17" t="n">
-        <v>0.637</v>
+        <v>-2.2419</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5873</v>
+        <v>-1.8081</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1064</v>
+        <v>-0.5935</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5192</v>
+        <v>-1.2146</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1738</v>
+        <v>-2.6364</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2917</v>
+        <v>-1.6091</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8822</v>
+        <v>-1.0273</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.131</v>
+        <v>0.1057</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4657</v>
+        <v>-0.5021</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5967</v>
+        <v>0.6077</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1853</v>
+        <v>4.1888</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8924</v>
+        <v>4.5157</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7071</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.173</v>
+        <v>-0.0233</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3262</v>
+        <v>0.1554</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4992</v>
+        <v>-0.1787</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.4392</v>
+        <v>-1.9593</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1975</v>
+        <v>-1.7153</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2417</v>
+        <v>-0.244</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7777</v>
+        <v>0.1047</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5754</v>
+        <v>0.2241</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2023</v>
+        <v>-0.1194</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6615</v>
+        <v>-2.064</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6221</v>
+        <v>-1.9394</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0395</v>
+        <v>-0.1246</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6179</v>
+        <v>0.7978</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9739</v>
+        <v>0.0507</v>
       </c>
       <c r="U18" t="n">
-        <v>0.356</v>
+        <v>0.7471</v>
       </c>
       <c r="V18" t="n">
-        <v>4.2036</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.5314</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6399</v>
+        <v>-0.5996</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1045</v>
+        <v>-0.1049</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5354</v>
+        <v>-0.4946</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7435</v>
+        <v>-0.7391</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1544</v>
+        <v>-0.1523</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7781</v>
+        <v>-0.7736</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0375</v>
+        <v>0.0697</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1766</v>
+        <v>0.2091</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1157</v>
+        <v>-0.7538</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2938</v>
+        <v>-0.2021</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4095</v>
+        <v>-0.5517</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0736</v>
+        <v>-0.4352</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.633</v>
+        <v>-0.9103</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5594</v>
+        <v>0.4751</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0393</v>
+        <v>1.1117</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3414</v>
+        <v>0.1961</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3807</v>
+        <v>0.9156</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.113</v>
+        <v>-1.5469</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2917</v>
+        <v>-1.1064</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1787</v>
+        <v>-0.4405</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8147</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4537</v>
+        <v>-2.7316</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4957</v>
+        <v>0.0765</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5474</v>
+        <v>-0.2164</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0517</v>
+        <v>0.2929</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.3524</v>
+        <v>0.0601</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>1.6342</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.5131</v>
+        <v>-1.5741</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3288</v>
+        <v>-1.1515</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1465</v>
+        <v>0.2466</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4753</v>
+        <v>-1.3981</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7137</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8874</v>
+        <v>-0.8875</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6046</v>
+        <v>1.6012</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4016</v>
+        <v>1.3872</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6844</v>
+        <v>-0.6734</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.046</v>
+        <v>0.1348</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.121</v>
+        <v>-0.0024</v>
       </c>
       <c r="U21" t="n">
-        <v>0.075</v>
+        <v>0.1372</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. NUNEZ</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4077</v>
+        <v>-1.2431</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3155</v>
+        <v>-0.2179</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0922</v>
+        <v>-1.0252</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.514</v>
+        <v>-1.0865</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3145</v>
+        <v>-2.6554</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1994</v>
+        <v>1.569</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1963</v>
+        <v>0.0011</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9453</v>
+        <v>-1.3767</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.749</v>
+        <v>1.3778</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7103</v>
+        <v>-1.0876</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2599</v>
+        <v>-1.2788</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4504</v>
+        <v>0.1912</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3992</v>
+        <v>0.3703</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5383</v>
+        <v>0.0785</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9376</v>
+        <v>0.2919</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>-2.348</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.5058</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. NUNEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4891</v>
+        <v>-1.3254</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0202</v>
+        <v>-1.101</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5093</v>
+        <v>-0.2244</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0704</v>
+        <v>-1.5087</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5022</v>
+        <v>-0.3159</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4318</v>
+        <v>-1.1929</v>
       </c>
       <c r="J23" t="n">
-        <v>1.368</v>
+        <v>0.1816</v>
       </c>
       <c r="K23" t="n">
-        <v>1.368</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.7524</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2976</v>
+        <v>-1.6904</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8658</v>
+        <v>-1.2499</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4318</v>
+        <v>-0.4405</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3061</v>
+        <v>0.4809</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3478</v>
+        <v>-0.3022</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0417</v>
+        <v>0.7831</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2534</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8268</v>
+        <v>-1.4202</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.988</v>
+        <v>1.0132</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8388</v>
+        <v>-2.4334</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4305</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9076</v>
+        <v>0.4999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4771</v>
+        <v>-0.4289</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1384</v>
+        <v>1.3617</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2109</v>
+        <v>1.3617</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9275</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5689</v>
+        <v>-1.2907</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1185</v>
+        <v>-0.8618</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4504</v>
+        <v>-0.4289</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2683</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0005</v>
+        <v>-0.244</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0434</v>
+        <v>-0.3485</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0429</v>
+        <v>0.1046</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0578</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.5812</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.6578</v>
+        <v>4.4482</v>
       </c>
       <c r="E25" t="n">
-        <v>9.158899999999999</v>
+        <v>8.857200000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.5011</v>
+        <v>-4.409</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.290800000000001</v>
+        <v>-8.317099999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.277200000000001</v>
+        <v>-9.331199999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9865000000000002</v>
+        <v>1.0142</v>
       </c>
       <c r="J25" t="n">
-        <v>8.1046</v>
+        <v>7.869400000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6143</v>
+        <v>2.4502</v>
       </c>
       <c r="L25" t="n">
-        <v>5.4904</v>
+        <v>5.419</v>
       </c>
       <c r="M25" t="n">
-        <v>-16.3956</v>
+        <v>-16.1864</v>
       </c>
       <c r="N25" t="n">
-        <v>-11.8919</v>
+        <v>-11.7817</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.5041</v>
+        <v>-4.4049</v>
       </c>
       <c r="P25" t="n">
-        <v>5.6708</v>
+        <v>5.6908</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.073499999999999</v>
+        <v>-9.105499999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>14.7442</v>
+        <v>14.7961</v>
       </c>
       <c r="S25" t="n">
-        <v>3.931699999999999</v>
+        <v>4.737900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8316</v>
+        <v>-0.8164</v>
       </c>
       <c r="U25" t="n">
-        <v>4.7634</v>
+        <v>5.5542</v>
       </c>
       <c r="V25" t="n">
-        <v>2.345899999999999</v>
+        <v>2.3367</v>
       </c>
       <c r="W25" t="n">
-        <v>10.959</v>
+        <v>10.9097</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.613099999999999</v>
+        <v>-8.572899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104707_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104707_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-10.9096</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.4471</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.5741</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.5058</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104707_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.572899999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
